--- a/Backtest/04-01-19/S&P500stock_04-01-19period252RS90.xlsx
+++ b/Backtest/04-01-19/S&P500stock_04-01-19period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="80">
   <si>
     <t>Stock</t>
   </si>
@@ -124,13 +124,133 @@
     <t>Industry</t>
   </si>
   <si>
-    <t>ORLY</t>
-  </si>
-  <si>
-    <t>2019-02-06</t>
+    <t>EM Rating</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>SNPS</t>
+  </si>
+  <si>
+    <t>MRK</t>
+  </si>
+  <si>
+    <t>LULU</t>
+  </si>
+  <si>
+    <t>KEYS</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>CDNS</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>ISRG</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>TPL</t>
+  </si>
+  <si>
+    <t>TSCO</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-05-22</t>
+  </si>
+  <si>
+    <t>2019-04-30</t>
+  </si>
+  <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-05-30</t>
+  </si>
+  <si>
+    <t>2019-04-22</t>
+  </si>
+  <si>
+    <t>2019-06-04</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2019-04-29</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Scientific &amp; Technical Instruments</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
+  </si>
+  <si>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
   </si>
   <si>
     <t>Specialty Retail</t>
@@ -491,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,106 +723,1557 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:37">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>97.9381443298969</v>
+        <v>96.51639344262296</v>
       </c>
       <c r="C2">
-        <v>423</v>
+        <v>92</v>
       </c>
       <c r="D2">
-        <v>346.13</v>
+        <v>16.79</v>
       </c>
       <c r="E2">
-        <v>1.96</v>
+        <v>1.93</v>
+      </c>
+      <c r="F2">
+        <v>0.1935882152323355</v>
       </c>
       <c r="G2">
-        <v>2.01</v>
+        <v>1.86</v>
+      </c>
+      <c r="H2">
+        <v>-0.03521483157561104</v>
       </c>
       <c r="I2">
-        <v>343.3659973144531</v>
+        <v>16.72039985656738</v>
       </c>
       <c r="J2">
-        <v>341.6330032348633</v>
+        <v>16.76680002212525</v>
       </c>
       <c r="K2">
-        <v>341.7273992919922</v>
+        <v>16.30727994918823</v>
       </c>
       <c r="L2">
-        <v>304.7159510803223</v>
+        <v>15.30714999198914</v>
       </c>
       <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1.03</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>10.41</v>
+      </c>
+      <c r="Y2">
+        <v>18.87</v>
+      </c>
+      <c r="Z2">
+        <v>12.27</v>
+      </c>
+      <c r="AA2">
+        <v>1933.59</v>
+      </c>
+      <c r="AB2">
+        <v>360.47</v>
+      </c>
+      <c r="AC2">
+        <v>336</v>
+      </c>
+      <c r="AD2">
+        <v>18.34</v>
+      </c>
+      <c r="AE2">
+        <v>211.43</v>
+      </c>
+      <c r="AF2">
+        <v>20.69</v>
+      </c>
+      <c r="AG2">
+        <v>16</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK2">
+        <v>85.07706518039639</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>90.57377049180327</v>
+      </c>
+      <c r="C3">
+        <v>346</v>
+      </c>
+      <c r="D3">
+        <v>115.15</v>
+      </c>
+      <c r="E3">
+        <v>1.11</v>
+      </c>
+      <c r="F3">
+        <v>-0.7324087476290022</v>
+      </c>
+      <c r="G3">
+        <v>1.37</v>
+      </c>
+      <c r="H3">
+        <v>-0.9299324042003921</v>
+      </c>
+      <c r="I3">
+        <v>113.0660003662109</v>
+      </c>
+      <c r="J3">
+        <v>108.4974998474121</v>
+      </c>
+      <c r="K3">
+        <v>101.9341999816895</v>
+      </c>
+      <c r="L3">
+        <v>93.97349987030029</v>
+      </c>
+      <c r="M3">
+        <v>1.04</v>
+      </c>
+      <c r="N3">
+        <v>1.11</v>
+      </c>
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3">
+        <v>4</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>79.14</v>
+      </c>
+      <c r="Y3">
+        <v>115.21</v>
+      </c>
+      <c r="Z3">
+        <v>14.25</v>
+      </c>
+      <c r="AA3">
+        <v>19.55</v>
+      </c>
+      <c r="AB3">
+        <v>291.09</v>
+      </c>
+      <c r="AC3">
+        <v>49.28</v>
+      </c>
+      <c r="AD3">
+        <v>4.06</v>
+      </c>
+      <c r="AE3">
+        <v>-39.41</v>
+      </c>
+      <c r="AF3">
+        <v>220.75</v>
+      </c>
+      <c r="AG3">
+        <v>-23.19</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK3">
+        <v>73.0001833319123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>94.4672131147541</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>79.36</v>
+      </c>
+      <c r="E4">
+        <v>0.67</v>
+      </c>
+      <c r="F4">
+        <v>-1.22928516672533</v>
+      </c>
+      <c r="G4">
+        <v>1.06</v>
+      </c>
+      <c r="H4">
+        <v>-1.495978215452805</v>
+      </c>
+      <c r="I4">
+        <v>78.8854965209961</v>
+      </c>
+      <c r="J4">
+        <v>77.99522857666015</v>
+      </c>
+      <c r="K4">
+        <v>75.51030487060547</v>
+      </c>
+      <c r="L4">
+        <v>68.90887386322021</v>
+      </c>
+      <c r="M4">
         <v>1.01</v>
       </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="b">
-        <v>1</v>
-      </c>
-      <c r="W2" t="b">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>217.64</v>
-      </c>
-      <c r="Y2">
-        <v>363.2</v>
-      </c>
-      <c r="Z2">
-        <v>28.28</v>
-      </c>
-      <c r="AA2">
-        <v>6.02</v>
-      </c>
-      <c r="AB2">
-        <v>3.95</v>
-      </c>
-      <c r="AC2">
-        <v>28.25</v>
-      </c>
-      <c r="AD2">
-        <v>73.47</v>
-      </c>
-      <c r="AE2">
-        <v>5.09</v>
-      </c>
-      <c r="AF2">
-        <v>18.36</v>
-      </c>
-      <c r="AG2">
-        <v>3.11</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>39</v>
+      <c r="N4">
+        <v>1.04</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>50.41</v>
+      </c>
+      <c r="Y4">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="Z4">
+        <v>195.33</v>
+      </c>
+      <c r="AA4">
+        <v>10.92</v>
+      </c>
+      <c r="AB4">
+        <v>103.48</v>
+      </c>
+      <c r="AC4">
+        <v>159.26</v>
+      </c>
+      <c r="AD4">
+        <v>6.61</v>
+      </c>
+      <c r="AE4">
+        <v>-4.11</v>
+      </c>
+      <c r="AF4">
+        <v>14.06</v>
+      </c>
+      <c r="AG4">
+        <v>137.04</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK4">
+        <v>60.56541788070746</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>99.38524590163934</v>
+      </c>
+      <c r="C5">
+        <v>81</v>
+      </c>
+      <c r="D5">
+        <v>163.87</v>
+      </c>
+      <c r="E5">
+        <v>3.77</v>
+      </c>
+      <c r="F5">
+        <v>2.271435058726069</v>
+      </c>
+      <c r="G5">
+        <v>2.68</v>
+      </c>
+      <c r="H5">
+        <v>1.462067636898513</v>
+      </c>
+      <c r="I5">
+        <v>153.6699981689453</v>
+      </c>
+      <c r="J5">
+        <v>147.6289985656738</v>
+      </c>
+      <c r="K5">
+        <v>148.7883990478516</v>
+      </c>
+      <c r="L5">
+        <v>138.1686500167847</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>1.03</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>6</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>8.888888888888888</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="Y5">
+        <v>171.45</v>
+      </c>
+      <c r="Z5">
+        <v>19.8</v>
+      </c>
+      <c r="AA5">
+        <v>17.11</v>
+      </c>
+      <c r="AB5">
+        <v>48.16</v>
+      </c>
+      <c r="AC5">
+        <v>201.82</v>
+      </c>
+      <c r="AD5">
+        <v>15.11</v>
+      </c>
+      <c r="AE5">
+        <v>133.8</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>29.09</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5">
+        <v>53.15298932245296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6">
+        <v>98.5655737704918</v>
+      </c>
+      <c r="C6">
+        <v>320</v>
+      </c>
+      <c r="D6">
+        <v>87.2</v>
+      </c>
+      <c r="E6">
+        <v>1.06</v>
+      </c>
+      <c r="F6">
+        <v>-0.7888719770717667</v>
+      </c>
+      <c r="G6">
+        <v>1.61</v>
+      </c>
+      <c r="H6">
+        <v>-0.491703389037234</v>
+      </c>
+      <c r="I6">
+        <v>85.83399963378906</v>
+      </c>
+      <c r="J6">
+        <v>85.47850036621094</v>
+      </c>
+      <c r="K6">
+        <v>80.3324006652832</v>
+      </c>
+      <c r="L6">
+        <v>66.09070018768311</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1.07</v>
+      </c>
+      <c r="P6">
+        <v>12</v>
+      </c>
+      <c r="Q6">
+        <v>10</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>21.11111111111111</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>50.25</v>
+      </c>
+      <c r="Y6">
+        <v>88.09</v>
+      </c>
+      <c r="Z6">
+        <v>14.06</v>
+      </c>
+      <c r="AA6">
+        <v>16.36</v>
+      </c>
+      <c r="AB6">
+        <v>28.57</v>
+      </c>
+      <c r="AC6">
+        <v>79.41</v>
+      </c>
+      <c r="AD6">
+        <v>4.29</v>
+      </c>
+      <c r="AE6">
+        <v>201.67</v>
+      </c>
+      <c r="AF6">
+        <v>-193.75</v>
+      </c>
+      <c r="AG6">
+        <v>88.23999999999999</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK6">
+        <v>45.26734887629468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7">
+        <v>93.64754098360656</v>
+      </c>
+      <c r="C7">
+        <v>147</v>
+      </c>
+      <c r="D7">
+        <v>29.75</v>
+      </c>
+      <c r="E7">
+        <v>2.51</v>
+      </c>
+      <c r="F7">
+        <v>0.8485616767684035</v>
+      </c>
+      <c r="G7">
+        <v>1.98</v>
+      </c>
+      <c r="H7">
+        <v>0.1838996760059678</v>
+      </c>
+      <c r="I7">
+        <v>29.32894020080566</v>
+      </c>
+      <c r="J7">
+        <v>28.91611747741699</v>
+      </c>
+      <c r="K7">
+        <v>27.1235680770874</v>
+      </c>
+      <c r="L7">
+        <v>26.66135851860047</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.08</v>
+      </c>
+      <c r="P7">
+        <v>7</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>4</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>19.4</v>
+      </c>
+      <c r="Y7">
+        <v>31.01</v>
+      </c>
+      <c r="Z7">
+        <v>19.23</v>
+      </c>
+      <c r="AA7">
+        <v>-0.2</v>
+      </c>
+      <c r="AB7">
+        <v>34.66</v>
+      </c>
+      <c r="AC7">
+        <v>59.52</v>
+      </c>
+      <c r="AD7">
+        <v>30.47</v>
+      </c>
+      <c r="AE7">
+        <v>70.63</v>
+      </c>
+      <c r="AF7">
+        <v>-76</v>
+      </c>
+      <c r="AG7">
+        <v>21.69</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK7">
+        <v>42.37407627351552</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>98.77049180327869</v>
+      </c>
+      <c r="C8">
+        <v>253</v>
+      </c>
+      <c r="D8">
+        <v>63.51</v>
+      </c>
+      <c r="E8">
+        <v>0.97</v>
+      </c>
+      <c r="F8">
+        <v>-0.8905057900687429</v>
+      </c>
+      <c r="G8">
+        <v>1.33</v>
+      </c>
+      <c r="H8">
+        <v>-1.002970573394252</v>
+      </c>
+      <c r="I8">
+        <v>62.48000030517578</v>
+      </c>
+      <c r="J8">
+        <v>60.91150016784668</v>
+      </c>
+      <c r="K8">
+        <v>54.97580009460449</v>
+      </c>
+      <c r="L8">
+        <v>47.0455500793457</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
+        <v>1.14</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8">
+        <v>18</v>
+      </c>
+      <c r="Q8">
+        <v>12</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>35.49</v>
+      </c>
+      <c r="Y8">
+        <v>63.56</v>
+      </c>
+      <c r="Z8">
+        <v>12.22</v>
+      </c>
+      <c r="AA8">
+        <v>49.99</v>
+      </c>
+      <c r="AB8">
+        <v>23.53</v>
+      </c>
+      <c r="AC8">
+        <v>33.33</v>
+      </c>
+      <c r="AD8">
+        <v>7.64</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>33.33</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK8">
+        <v>38.77540029872071</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>90.77868852459017</v>
+      </c>
+      <c r="C9">
+        <v>95</v>
+      </c>
+      <c r="D9">
+        <v>158.37</v>
+      </c>
+      <c r="E9">
+        <v>1.59</v>
+      </c>
+      <c r="F9">
+        <v>-0.1903617449784629</v>
+      </c>
+      <c r="G9">
+        <v>1.73</v>
+      </c>
+      <c r="H9">
+        <v>-0.2725888814556552</v>
+      </c>
+      <c r="I9">
+        <v>157.7899963378906</v>
+      </c>
+      <c r="J9">
+        <v>159.3814971923828</v>
+      </c>
+      <c r="K9">
+        <v>157.5717984008789</v>
+      </c>
+      <c r="L9">
+        <v>146.2362494277954</v>
+      </c>
+      <c r="M9">
+        <v>0.99</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>112.52</v>
+      </c>
+      <c r="Y9">
+        <v>166.99</v>
+      </c>
+      <c r="Z9">
+        <v>117.78</v>
+      </c>
+      <c r="AA9">
+        <v>-97.84999999999999</v>
+      </c>
+      <c r="AB9">
+        <v>52.58</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>2.32</v>
+      </c>
+      <c r="AE9">
+        <v>235.71</v>
+      </c>
+      <c r="AF9">
+        <v>-65</v>
+      </c>
+      <c r="AG9">
+        <v>-14.89</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK9">
+        <v>23.52716700755287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <v>91.59836065573771</v>
+      </c>
+      <c r="C10">
+        <v>317</v>
+      </c>
+      <c r="D10">
+        <v>190.19</v>
+      </c>
+      <c r="E10">
+        <v>1.28</v>
+      </c>
+      <c r="F10">
+        <v>-0.5404337675236029</v>
+      </c>
+      <c r="G10">
+        <v>1.92</v>
+      </c>
+      <c r="H10">
+        <v>0.07434242221517819</v>
+      </c>
+      <c r="I10">
+        <v>188.1399993896484</v>
+      </c>
+      <c r="J10">
+        <v>185.334334564209</v>
+      </c>
+      <c r="K10">
+        <v>180.669333190918</v>
+      </c>
+      <c r="L10">
+        <v>174.0346668243408</v>
+      </c>
+      <c r="M10">
+        <v>1.02</v>
+      </c>
+      <c r="N10">
+        <v>1.04</v>
+      </c>
+      <c r="O10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10">
+        <v>2</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>131.19</v>
+      </c>
+      <c r="Y10">
+        <v>193.71</v>
+      </c>
+      <c r="Z10">
+        <v>56.9</v>
+      </c>
+      <c r="AA10">
+        <v>16.03</v>
+      </c>
+      <c r="AB10">
+        <v>15.89</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>4.36</v>
+      </c>
+      <c r="AE10">
+        <v>-0.78</v>
+      </c>
+      <c r="AF10">
+        <v>14.23</v>
+      </c>
+      <c r="AG10">
+        <v>-11.76</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK10">
+        <v>4.970417993707724</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>97.54098360655738</v>
+      </c>
+      <c r="C11">
+        <v>237</v>
+      </c>
+      <c r="D11">
+        <v>24.5</v>
+      </c>
+      <c r="E11">
+        <v>1.41</v>
+      </c>
+      <c r="F11">
+        <v>-0.3936293709724153</v>
+      </c>
+      <c r="G11">
+        <v>2.34</v>
+      </c>
+      <c r="H11">
+        <v>0.8412431987507047</v>
+      </c>
+      <c r="I11">
+        <v>24.16366691589355</v>
+      </c>
+      <c r="J11">
+        <v>23.94416666030884</v>
+      </c>
+      <c r="K11">
+        <v>23.30733329772949</v>
+      </c>
+      <c r="L11">
+        <v>20.71388326644897</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>1.04</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11">
+        <v>3.888888888888889</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>14.3</v>
+      </c>
+      <c r="Y11">
+        <v>25.55</v>
+      </c>
+      <c r="Z11">
+        <v>3.76</v>
+      </c>
+      <c r="AA11">
+        <v>296320</v>
+      </c>
+      <c r="AB11">
+        <v>185.86</v>
+      </c>
+      <c r="AC11">
+        <v>921.1799999999999</v>
+      </c>
+      <c r="AD11">
+        <v>19.29</v>
+      </c>
+      <c r="AE11">
+        <v>170.67</v>
+      </c>
+      <c r="AF11">
+        <v>348.95</v>
+      </c>
+      <c r="AG11">
+        <v>-251.55</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK11">
+        <v>80.78853654514286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>98.97540983606558</v>
+      </c>
+      <c r="C12">
+        <v>318</v>
+      </c>
+      <c r="D12">
+        <v>141.96</v>
+      </c>
+      <c r="E12">
+        <v>3.29</v>
+      </c>
+      <c r="F12">
+        <v>1.72938805607553</v>
+      </c>
+      <c r="G12">
+        <v>3.08</v>
+      </c>
+      <c r="H12">
+        <v>2.192449328837109</v>
+      </c>
+      <c r="I12">
+        <v>137.5360015869141</v>
+      </c>
+      <c r="J12">
+        <v>138.4460006713867</v>
+      </c>
+      <c r="K12">
+        <v>137.4750006103516</v>
+      </c>
+      <c r="L12">
+        <v>129.1075999832153</v>
+      </c>
+      <c r="M12">
+        <v>0.99</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>78.02</v>
+      </c>
+      <c r="Y12">
+        <v>154.06</v>
+      </c>
+      <c r="Z12">
+        <v>7.79</v>
+      </c>
+      <c r="AA12">
+        <v>145.75</v>
+      </c>
+      <c r="AB12">
+        <v>258.93</v>
+      </c>
+      <c r="AC12">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="AD12">
+        <v>12.2</v>
+      </c>
+      <c r="AE12">
+        <v>1.55</v>
+      </c>
+      <c r="AF12">
+        <v>-2.13</v>
+      </c>
+      <c r="AG12">
+        <v>83.8</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK12">
+        <v>72.26006878162119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <v>95.49180327868852</v>
+      </c>
+      <c r="C13">
+        <v>456</v>
+      </c>
+      <c r="D13">
+        <v>209.53</v>
+      </c>
+      <c r="E13">
+        <v>1.64</v>
+      </c>
+      <c r="F13">
+        <v>-0.1338985155356986</v>
+      </c>
+      <c r="G13">
+        <v>1.93</v>
+      </c>
+      <c r="H13">
+        <v>0.09260196451364312</v>
+      </c>
+      <c r="I13">
+        <v>207.7339996337891</v>
+      </c>
+      <c r="J13">
+        <v>208.4979995727539</v>
+      </c>
+      <c r="K13">
+        <v>194.6405999755859</v>
+      </c>
+      <c r="L13">
+        <v>170.0431497955322</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1.07</v>
+      </c>
+      <c r="P13">
+        <v>14</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>130.79</v>
+      </c>
+      <c r="Y13">
+        <v>219.39</v>
+      </c>
+      <c r="Z13">
+        <v>8.65</v>
+      </c>
+      <c r="AA13">
+        <v>12.98</v>
+      </c>
+      <c r="AB13">
+        <v>231.65</v>
+      </c>
+      <c r="AC13">
+        <v>4.9</v>
+      </c>
+      <c r="AD13">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AE13">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="AF13">
+        <v>80.92</v>
+      </c>
+      <c r="AG13">
+        <v>-35.78</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK13">
+        <v>61.59721673988506</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>95.90163934426229</v>
+      </c>
+      <c r="C14">
+        <v>486</v>
+      </c>
+      <c r="D14">
+        <v>257.88</v>
+      </c>
+      <c r="E14">
+        <v>1.91</v>
+      </c>
+      <c r="F14">
+        <v>0.1710029234552297</v>
+      </c>
+      <c r="G14">
+        <v>2.03</v>
+      </c>
+      <c r="H14">
+        <v>0.2751973874982921</v>
+      </c>
+      <c r="I14">
+        <v>255.8553375244141</v>
+      </c>
+      <c r="J14">
+        <v>248.3248344421387</v>
+      </c>
+      <c r="K14">
+        <v>241.3767343139648</v>
+      </c>
+      <c r="L14">
+        <v>238.8305503845215</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>1.06</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>136.33</v>
+      </c>
+      <c r="Y14">
+        <v>292.66</v>
+      </c>
+      <c r="Z14">
+        <v>4.22</v>
+      </c>
+      <c r="AA14">
+        <v>99.97</v>
+      </c>
+      <c r="AB14">
+        <v>49.77</v>
+      </c>
+      <c r="AC14">
+        <v>44.28</v>
+      </c>
+      <c r="AD14">
+        <v>25.62</v>
+      </c>
+      <c r="AE14">
+        <v>23.93</v>
+      </c>
+      <c r="AF14">
+        <v>-3.12</v>
+      </c>
+      <c r="AG14">
+        <v>20.17</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK14">
+        <v>42.18720503301021</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>97.74590163934425</v>
+      </c>
+      <c r="C15">
+        <v>89</v>
+      </c>
+      <c r="D15">
+        <v>19.55</v>
+      </c>
+      <c r="E15">
+        <v>1.48</v>
+      </c>
+      <c r="F15">
+        <v>-0.314580849752545</v>
+      </c>
+      <c r="G15">
+        <v>1.39</v>
+      </c>
+      <c r="H15">
+        <v>-0.8934133196034627</v>
+      </c>
+      <c r="I15">
+        <v>19.07200012207031</v>
+      </c>
+      <c r="J15">
+        <v>18.49579992294311</v>
+      </c>
+      <c r="K15">
+        <v>18.47423992156983</v>
+      </c>
+      <c r="L15">
+        <v>17.42829995632172</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>1.03</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>11.65</v>
+      </c>
+      <c r="Y15">
+        <v>19.72</v>
+      </c>
+      <c r="Z15">
+        <v>2.06</v>
+      </c>
+      <c r="AA15">
+        <v>11.91</v>
+      </c>
+      <c r="AB15">
+        <v>11.86</v>
+      </c>
+      <c r="AC15">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="AD15">
+        <v>8.76</v>
+      </c>
+      <c r="AE15">
+        <v>15.63</v>
+      </c>
+      <c r="AF15">
+        <v>-43.53</v>
+      </c>
+      <c r="AG15">
+        <v>198.25</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK15">
+        <v>23.3870421796181</v>
       </c>
     </row>
   </sheetData>
